--- a/04_DESIGN_TABLES/DesignTable_4000.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_4000.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,45 +413,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>OMi 4000 - Design Table SKELETON (no dimensional source) | OMi catalog 11 SKUs | ALL MISSING | GENERATED 2026-09-23</t>
+          <t>OMi 4000 O-Ring (Buna-N) - Design Table v1 | AW s218 double-pass 13 rows | single-source | GENERATED 2026-10-14 (staged, newtypes_20261014)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
+          <t>ID@DRIVE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>W@DRIVE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>$PRP@TubeOD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>$PRP@PartNo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>$PRP@Material</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>$PRP@Hardness</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>$PRP@Temperature</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$PRP@Tolerance</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>$PRP@DataStatus</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>$PRP@AxialSource</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>$COMMENT</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>$PRP@ScopeAction</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
         </is>
       </c>
     </row>
@@ -461,34 +496,65 @@
           <t>4000-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1/8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>4000-02</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.005, W +/-0.003 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1114: "02 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>4000-02</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
         </is>
       </c>
     </row>
@@ -498,34 +564,65 @@
           <t>4000-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3/16</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>4000-03</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.005, W +/-0.003 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1115: "03 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>4000-03</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
         </is>
       </c>
     </row>
@@ -535,330 +632,735 @@
           <t>4000-04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>4000-04</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.005, W +/-0.003 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1116: "04 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>4000-04</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4000-06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4000-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
+          <t>4000-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.07199999999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>5/16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BUILD</t>
+          <t>4000-05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4000-06</t>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.005, W +/-0.003 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-10-14) | OMi parts file row 1117: "05 Buna O-Ring" (no sizes) - asked in the 2026-10-14 request ("do you sell it?")</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4000-08</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4000-08</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
+          <t>4000-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>4000-06</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.005, W +/-0.003 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1118: "06 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4000-08</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4000-06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4000-10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4000-10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
+          <t>4000-08</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>4000-08</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.009, W +/-0.003 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1119: "08 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>4000-10</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4000-08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4000-12</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4000-12</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
+          <t>4000-10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>4000-10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.009, W +/-0.003 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1120: "10 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>4000-12</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4000-10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4000-16</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4000-16</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
+          <t>4000-12</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>4000-12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.009, W +/-0.004 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1121: "12 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4000-16</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4000-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4000-20</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4000-20</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
+          <t>4000-14</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>7/8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BUILD</t>
+          <t>4000-14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4000-20</t>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.010, W +/-0.004 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-10-14) | OMi parts file row 1122: "14 Buna O-Ring" (no sizes) - asked in the 2026-10-14 request ("do you sell it?")</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>DROP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4000-24</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4000-24</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
+          <t>4000-16</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>4000-16</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.010, W +/-0.004 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1123: "16 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4000-24</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4000-16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>4000-20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4000-20</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.014, W +/-0.004 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1124: "20 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4000-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4000-24</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1 1/2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4000-24</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.014, W +/-0.004 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1125: "24 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4000-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>4000-32</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="n">
+        <v>2.337</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>4000-32</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way lists no carbon-steel series for this root -&gt; no dimensions</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Buna-N (nitrile), Air-Way compound CH</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>90 pts ± 5 pts</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-35°C to 125°C (-30°F to 250°F)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>I.D. +/-0.018, W +/-0.004 (Air-Way)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Air-Way s218 only (O-rings For SAE J-1926/2/3 Inch Stud Ends; double-pass 33 rows, parts.air-way.com/api/series/218 fetched twice 2026-10-14, identical; rendered page cross-check 25 rows); Air-Way part numbers printed as 4000-n / 4001-n; config names zero-padded to 4000-nn / 4001-nn [user 2026-10-14: "use airway sizes"]</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OMi parts file row 1126: "32 Buna O-Ring" (no sizes)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>4000-32</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MISSING: needs a dimensional source (Air-Way sibling family, Parker/Brennan catalog, or a STEP measurement) before any geometry is modelled</t>
         </is>
       </c>
     </row>
